--- a/www/download/COUNTRY.NOR.EXI382.xlsx
+++ b/www/download/COUNTRY.NOR.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Noruega</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14291840490798</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14323312883436</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14323312883436</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14323312883436</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14323312883436</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14323312883436</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14323312883436</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.14323312883436</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2.354</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.135</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2.204</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2.263</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.332</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.348</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.364</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.372</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.379</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.345</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.355</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.366</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.522</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.447</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.498</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.499</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.533</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.581</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.562</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2.433</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2.251</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2.171</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2.186</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2.121</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2.155</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2.316</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.162</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.014</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.076</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2.139</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.171</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.191</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.195</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.202</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.169</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.235</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.324</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.257</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.296</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.306</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.355</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.402</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.383</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2.255</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2.082</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1.999</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2.014</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1.956</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>1.983</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2.134</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4157.117</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3918.203</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4072.668</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4284.869</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4400.057</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4434.13</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4274.174</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4282.962</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>4410.964</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>4113.455</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>4127.597</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>4326.914</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>4449.578</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>4575.947</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4454.165</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>4488.58</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>4478.093</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>4568.796</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>4659.401</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>4621.534</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>4391.906</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4055.965</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>3914.062</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>3921.409</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>3806.028</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>3845.528</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>4109.37</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3761.578</t>
+          <t>7350431757.64257</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2991.935</t>
+          <t>6199257768.77376</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3201.736</t>
+          <t>6241922762.26904</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3383.165</t>
+          <t>6576738577.03164</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3492.403</t>
+          <t>7196795769.50214</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3571.068</t>
+          <t>6606726649.56616</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3466.248</t>
+          <t>6455436357.03821</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3482.188</t>
+          <t>6986613545.69893</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3592.404</t>
+          <t>7792898281.2774</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3347.189</t>
+          <t>6647024669.35339</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3355.997</t>
+          <t>6868021747.67897</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3572.076</t>
+          <t>7144611612.34149</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3570.838</t>
+          <t>7309627627.41682</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3742.079</t>
+          <t>9109387916.90491</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3651.025</t>
+          <t>7776005613.35401</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3653.77</t>
+          <t>8051573841.55644</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3687.283</t>
+          <t>8560718587.05565</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3820.382</t>
+          <t>9536486624.31259</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3918.987</t>
+          <t>10759759912.3215</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4252.414</t>
+          <t>9458273326.44399</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4020.262</t>
+          <t>8292489977.76154</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3703.207</t>
+          <t>7553119512.44632</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3551.175</t>
+          <t>7283778437.83299</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3557.714</t>
+          <t>7049140479.31068</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3456.734</t>
+          <t>7153471398.76235</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3486.542</t>
+          <t>7455241867.42887</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>3732.784</t>
+          <t>7474234252.71612</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4602128250.09241</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3168466552.04352</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3568716656.38448</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3810978131.84161</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3010917440.82764</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3666931270.13895</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3662516259.06501</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3586323540.59336</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3257800162.29318</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3866250491.58381</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3655037594.54309</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3821731194.98388</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4492780272.89494</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5008104418.7649</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4123635264.96701</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4017888480.38519</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4193589556.11435</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4796527535.3748</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>5540797656.22997</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5129195889.16656</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>3850792207.30016</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>4511809110.9449</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3984697019.17042</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>4079803138.314</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>4143408115.02678</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>5310143725.45895</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4923284059.8088</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6973372.99910857</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27387781.9880504</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5760789.136716</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5929179.24748867</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5640956.97764137</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4596440.18637828</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5215441.43650847</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4250969.55987076</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4195050.12272614</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4437070.48451898</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3695634.96143049</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3145309.4871415</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3473823.42599664</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>36128705455.0051</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3210584.31887837</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2720827.62071738</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2875630.02927664</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4215987.58083065</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4813032.09975445</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3505290.75750447</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>3490695.80029453</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3359985.83036539</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2921691.75869538</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2877035.92657833</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3041428.64084542</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3012283.79924241</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3187011.00420639</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8598.1189651664</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>18078.4236882611</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20192.8502779986</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>21675.5972384948</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>22996.3692529467</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>27602.070581496</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>26579.6903766499</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>26058.2970476506</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>24912.7599638194</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>22524.3714975796</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>24164.7375599942</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>26924.442867472</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>28728.3259632796</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>29866.8856277388</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>29310.3713230429</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>34284.552257314</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>35736.1343307639</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>40932.6520685389</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>40049.5571750624</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>40977.7273931491</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>44053.1070442086</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>36852.8015134705</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>36976.1082919789</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>36139.3128497096</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>37786.9689475723</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>35516.1119455761</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>36400.9154206358</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>27399.4888362222</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>47108.6087948424</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>51662.0478580044</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>55961.0806617143</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>64593.3639813059</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>70882.3378671841</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>69542.8115825326</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>72958.6670885441</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>74755.5708634611</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>62312.0128889796</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>69022.0511208595</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>76806.7889578065</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>81413.9903583233</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>101947.801672448</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>87209.062372903</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>104133.900933611</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>115264.175464367</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>141725.057060556</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>156199.211369579</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>142122.273997873</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>140757.945030406</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>116857.618509453</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>119141.42417439</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>112140.931961566</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>121250.415525299</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>120211.727059777</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>118322.062419773</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.182643861811621</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.0557151382679737</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.102832668356579</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.112258091503229</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.159913238617353</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.0261426416467558</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.0535883652610487</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.0290368505281084</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.102708521406252</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.134254490937296</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.0818160105902797</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.0653251582192966</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.205205288684157</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.252795331906827</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.114610103609605</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.0906243371768689</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.120733455036115</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.203510879105031</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.292703462001963</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.170939375570493</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.0440090131127138</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.179219129465781</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.108796765193049</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.127969194870229</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-0.165726779984467</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.343418546375755</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.241810228930002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2128.38024413602</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1638.21237373608</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1771.60278811784</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1835.46603662357</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1407.8918174634</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1689.20732915952</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1671.38970431529</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1634.1581794377</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1479.13741761339</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1782.66806140852</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1676.46894530002</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1744.92338370133</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2009.92272755059</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2155.22847990871</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1827.04265173533</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1750.25635144887</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1818.39803838089</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2037.17457437847</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2306.7434039262</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2152.51426069588</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1707.74175988599</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2167.11462780082</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1993.6724618302</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2025.6406713202</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2117.9248834191</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2677.52842372465</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2307.1618083965</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>11055155258.2168</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>7021883895.24954</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>6882594376.60249</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>4848992482.00461</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>5985829857.3861</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>10158604091.2681</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>10598517871.9916</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>9743963763.61095</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>9130781287.01504</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>10995055776.12</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>12976406155.9718</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>13513696833.6577</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>10779753008.2392</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>15045365089.1171</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>10680377268.973</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>10880180225.7168</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>12192982022.3473</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>13197741198.994</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>12666041541.7632</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>9938686114.70746</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>7032390440.05495</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>6038118801.29916</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>6237970577.76586</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>7777240914.59418</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>5431943290.57583</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>6445854822.13984</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>6073886023.54547</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11059433531.7648</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>7260503599.38321</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7136775370.3916</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5299848032.12857</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6308473223.43145</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10345155735.7265</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10732575627.4043</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10028802674.2181</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>9591574821.21476</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>11669203991.3402</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>13731111738.0267</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>14142448848.0602</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>11201049550.5132</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>15827863037.8659</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>11533050548.4692</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>12199541358.588</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>13391580131.9175</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14445711591.8016</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>14087064059.7107</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>11190100195.5808</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>8241744339.88094</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7426247077.72576</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>7756752579.87207</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>9440507249.37283</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>7119404299.81174</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>8230281053.47801</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>9513149634.31252</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-4278273.54801324</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-238619704.133674</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-254180993.78911</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-450855550.123967</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-322643366.045357</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-186551644.458331</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-134057755.412692</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-284838910.607111</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-460793534.19972</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-674148215.22017</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-754705582.054963</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-628752014.402498</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-421296542.273966</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-782497948.748807</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-852673279.49624</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-1319361132.87124</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-1198598109.57012</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-1247970392.80758</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-1421022517.94755</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-1251414080.87336</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-1209353899.826</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-1388128276.4266</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1518782002.10621</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-1663266334.77865</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1687461009.23591</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-1784426231.33817</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-3439263610.76705</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>1739.64465694346</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1546.93914482107</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>1589.42414614773</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1629.42012233321</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>1633.03235761684</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>1645.04698728623</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>1581.82266234688</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>1586.70737264208</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>1631.05743473312</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>1543.33686831395</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>1539.30694431708</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>1630.93598758049</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1597.47595401072</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>1610.39678099515</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>1617.64510412077</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>1591.64052970921</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>1598.85656057627</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>1622.58738585629</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>1631.55162364681</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>1784.56481706594</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>1782.89778938995</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>1778.72623075379</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>1776.76734712861</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>1766.42106551497</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>1766.92801224107</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>1758.01550456937</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>1749.26648332959</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1765.6492338911</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>1835.22388758704</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>1847.85299455566</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>1893.44631020783</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1886.73598902261</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1888.63191072521</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1807.72035188682</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>1805.55710130293</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1853.96940147954</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>1754.21339929168</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1752.47187194846</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1828.63409686361</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1823.59754098362</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1814.771762839</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1820.1066525011</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1797.01337176739</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1791.95398159296</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>1803.85186354971</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1805.26966292118</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>1803.82536468551</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1805.06021723346</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1802.04628701337</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>1803.26845625955</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>1793.90311089439</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1794.18640663908</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>1784.15345901696</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1774.56194392866</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>52987.1146466028</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>59699.9810444974</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>67687.0563240179</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>58381.7640721068</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>69343.5246915036</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>103245.42197263</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>106728.621013302</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>101448.225275627</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>95598.3993841672</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>103477.937720834</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>128003.464028686</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>146857.912830912</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>147781.62592016</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>168622.898187808</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>127934.98054982</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>155976.061709785</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>179318.853069057</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>197481.750504102</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>188092.061482187</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>177998.366722057</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>160396.032046973</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>143852.931435257</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>154826.021227607</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>170277.431598257</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>159552.480201355</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>167417.218455763</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>169046.902698273</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1494945574.75813</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1549071780.07334</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1513205310.32593</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1557712129.47253</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1763346053.18885</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1813409135.27703</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1629211194.8881</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1797734954.46451</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1970620228.23446</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1628394769.40464</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1633840168.50227</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1716570933.2343</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1709680776.90478</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2083042516.57162</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1713584517.48314</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2037309583.49306</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2154027475.22342</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2478541396.24763</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2796134384.45398</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2646615705.67044</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2251396108.22359</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2014044585.6534</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1902848723.90718</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>1709829492.61931</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1906781509.485</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2019262258.71156</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1968911738.22699</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>43804.863658362</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>44936.4049638868</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>52701.1875633889</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>55155.9923578031</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>55002.248555281</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>62470.4982320405</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>64436.1215612591</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>65921.1034303696</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>61970.8655956926</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>66838.3122602749</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>76071.1374694931</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>85897.8507340955</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>96457.1993030459</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>98968.8342753117</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>86589.2913307015</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>108299.755959097</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>119038.390914529</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>129284.949612159</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>132242.554556462</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>132217.077057182</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>134268.758090515</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>135225.580687195</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>138674.264340155</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>142343.964501328</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>151289.517600598</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>155705.823446634</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>156471.581914882</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4157.117</t>
+          <t>7348114708.64005</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3918.203</t>
+          <t>5571911636.74766</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4072.668</t>
+          <t>5590629123.56792</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4284.869</t>
+          <t>5798974638.10043</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4400.057</t>
+          <t>5118356387.61952</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4434.13</t>
+          <t>5646167973.98998</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4274.174</t>
+          <t>5406837531.65859</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4282.962</t>
+          <t>5596819271.84967</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4410.964</t>
+          <t>5388834861.43096</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4113.455</t>
+          <t>5904115434.20907</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4127.597</t>
+          <t>5924534362.52239</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4326.914</t>
+          <t>6159916520.14492</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4449.578</t>
+          <t>6115843102.98267</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4575.947</t>
+          <t>7583060000.76961</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4454.165</t>
+          <t>6308231493.51907</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>4488.58</t>
+          <t>7038905176.37418</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>4478.093</t>
+          <t>7395722473.96752</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4568.796</t>
+          <t>8240701406.56716</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>4659.401</t>
+          <t>9064416261.89845</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>4621.534</t>
+          <t>7718471804.59192</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>4391.906</t>
+          <t>6758196657.65976</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>4055.965</t>
+          <t>7137176488.49991</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>3914.062</t>
+          <t>6585037547.50743</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3921.409</t>
+          <t>6710771320.56214</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>3806.028</t>
+          <t>6584585636.80844</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>3845.528</t>
+          <t>7328627774.85303</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>4109.37</t>
+          <t>6817520450.84598</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3761.578</t>
+          <t>9182.25098824076</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2991.935</t>
+          <t>14763.5760806106</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3201.736</t>
+          <t>14985.8687606289</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3383.165</t>
+          <t>3225.77171430364</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3492.403</t>
+          <t>14341.2761362226</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3571.068</t>
+          <t>40774.9237405891</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3466.248</t>
+          <t>42292.4994520426</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3482.188</t>
+          <t>35527.1218452572</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3592.404</t>
+          <t>33627.5337884746</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3347.189</t>
+          <t>36639.6254605592</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3355.997</t>
+          <t>51932.326559193</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3572.076</t>
+          <t>60960.0620968162</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3570.838</t>
+          <t>51324.4266171144</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3742.079</t>
+          <t>69654.0639124965</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3651.025</t>
+          <t>41345.6892191183</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3653.77</t>
+          <t>47676.3057506876</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3687.283</t>
+          <t>60280.4621545282</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3820.382</t>
+          <t>68196.8008919429</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3918.987</t>
+          <t>55849.5069257248</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>4252.414</t>
+          <t>45781.289664875</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>4020.262</t>
+          <t>26127.2739564577</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>3703.207</t>
+          <t>8627.3507480614</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>3551.175</t>
+          <t>16151.7568874518</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3557.714</t>
+          <t>27933.467096929</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>3456.734</t>
+          <t>8262.96260075731</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3486.542</t>
+          <t>11711.3950091292</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3732.784</t>
+          <t>12575.3207833917</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5675.147</t>
+          <t>-5853169133.88192</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4759.519</t>
+          <t>-4022839856.67432</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4839.499</t>
+          <t>-4077423813.24199</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5084.102</t>
+          <t>-4241262508.6279</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5523.746</t>
+          <t>-3355010334.43067</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5120.298</t>
+          <t>-3832758838.71295</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4964.079</t>
+          <t>-3777626336.7705</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5345.516</t>
+          <t>-3799084317.38516</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5961.548</t>
+          <t>-3418214633.19651</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5085.565</t>
+          <t>-4275720664.80444</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5249.188</t>
+          <t>-4290694194.02012</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5446.672</t>
+          <t>-4443345586.91062</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>5588.321</t>
+          <t>-4406162326.07789</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>6897.264</t>
+          <t>-5500017484.19799</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5900.704</t>
+          <t>-4594646976.03593</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6102.933</t>
+          <t>-5001595592.88112</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>6429.304</t>
+          <t>-5241694998.7441</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>7098.402</t>
+          <t>-5762160010.31953</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>7943.979</t>
+          <t>-6268281877.44447</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>7010.115</t>
+          <t>-5071856098.92149</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>6239.762</t>
+          <t>-4506800549.43616</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>5683.949</t>
+          <t>-5123131902.84651</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>5506.293</t>
+          <t>-4682188823.60026</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5333.175</t>
+          <t>-5000941827.94283</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>5396.04</t>
+          <t>-4677804127.32344</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>5574.723</t>
+          <t>-5309365516.14148</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>5585.291</t>
+          <t>-4848608712.61899</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>47461.7457446329</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>49986.8567238237</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>54113.4551046224</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>52875.5258555771</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>58825.3907387377</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>68782.6869618726</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>70888.1113728841</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>78910.7512385935</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>76067.8839313112</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>76849.9894376731</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>84255.0865425163</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>96101.2254570707</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>107927.896586076</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>115652.824875912</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>108171.07201628</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>119988.069743637</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>131218.366987733</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>146014.924478508</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>152252.42390159</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>149476.892971975</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>137018.219436601</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>133607.684116974</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>137983.897577703</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>142819.317719153</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>139896.461718046</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>147344.934663114</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>150092.655241901</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2306.608</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2379.03</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2439.745</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2547.391</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2562.185</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2572.705</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2467.307</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2495.375</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2597.032</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2402.748</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2404.506</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2504.527</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2579.328</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2668.709</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2613.462</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2650.862</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2654.138</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2754.303</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>2758.808</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2727.078</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>2595.306</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2381.989</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2260.555</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>2271.705</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2229.337</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>2202.624</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2299.393</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>71911.9890032507</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>76487.7878507885</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>82583.8815209825</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>82423.9993062133</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>90319.7709603358</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>101898.911410159</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>106252.649843664</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>119017.573669313</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>117132.542306395</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>118098.667649002</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>129821.99274502</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>141962.294779231</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>161443.564713639</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>172122.265759009</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>161472.229757147</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>185060.277752672</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>199442.44419697</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>219308.917508473</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>241292.027846066</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>236399.329883004</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>205592.493537299</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>208472.998907364</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>210531.206980142</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>210595.369272763</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>215400.061591489</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>228789.260466344</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>232689.712134981</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4344.458</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2885.217</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3305.225</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3532.051</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2753.116</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3386.336</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3359.702</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>3318.038</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2994.45</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>3591.526</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>3433.484</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>3542.882</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>4153.278</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>4618.323</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>3807.979</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>3707.488</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>3829.55</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>4400.91</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>5079.003</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>4728.86</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>3559.308</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>4205.537</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>3745.011</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>3809.358</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>3884.172</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>4933.819</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4563.317</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-13.42</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-4.22</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-6.8</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-14.02</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-18.97</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-4.12</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-3.71</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-13.19</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-22.84</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-10.08</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>12.95</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-11.94</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-5.18</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-6.61</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-29.33</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-18.2</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>6.903</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>30.023</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>5.786</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>5.968</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>5.648</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>4.623</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5.373</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>4.261</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4.141</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>4.446</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>3.658</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>3.107</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>3.496</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>42667.271</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>3.137</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>2.628</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2.754</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>4.108</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>4.499</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>3.346</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3.303</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2.876</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>2.851</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>3.026</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2.961</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>3.149</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>56115.1548285195</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>65029.9826341373</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>73620.4975560453</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>68763.9499596165</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>77141.5011119847</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>101725.632573704</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>107118.53344068</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>108958.924203438</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>106193.679467121</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>116498.122249803</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>145072.694803586</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>161268.103042188</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>160230.354589628</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>173581.775562802</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>145116.690969259</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>173362.132389066</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>195713.900524971</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>220557.279016294</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>192167.822170315</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>175437.782099985</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>179747.295383821</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>160862.194443999</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>180867.780479456</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>194996.315851399</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>184293.00728735</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>180872.659117617</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>183487.776770172</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3761577773.94317</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2991934999.99897</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3201735999.9999</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3383165000.00053</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3492402999.99986</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3571068000.00043</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3466247999.9997</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3482187999.99971</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3592403999.99936</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3347189000.00015</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3355997000.00008</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3572075999.99994</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3570838000.00105</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3742078999.99918</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3651025000.00092</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3653769999.9997</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3687283000.00129</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3820381999.99918</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3918986999.99909</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>4252414346.69369</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>4020261772.04557</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>3703206609.76558</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3551174873.2103</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>3557714015.47493</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>3456734429.96188</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>3486541886.2155</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>3732783614.219</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4157116788.06015</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3918202999.9989</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4072668000.0005</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4284869000.0004</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4400057000.00028</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4434130000.0001</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4274174000.00003</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4282962000.00007</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4410963999.99973</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4113455000.00015</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4127597000.00018</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4326913999.99986</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4449578000.00096</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4575946999.99934</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4454165000.00103</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>4488579999.99975</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>4478093000.00107</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>4568795999.99923</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>4659400999.99904</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>4621534090.24247</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>4391906228.3783</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>4055965284.58314</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>3914062462.73114</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>3921408518.47882</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>3806027827.0395</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>3845528269.2394</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4109370153.98039</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2306608239.12881</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2379030316.61819</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2439744783.86461</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2547390701.76924</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2562185381.78959</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2572704862.4676</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2467307486.01689</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2495375236.36515</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2597031927.67426</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2402747818.03062</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2404506101.94687</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2504527135.90774</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2579327757.13844</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2668709306.03337</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2613462474.38029</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2650862030.99653</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2654137663.86993</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2754302570.38085</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2758807909.59223</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2727078135.45621</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2595306066.55591</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2381989447.92964</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2260555320.35504</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>2271704797.23382</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2229336703.22953</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>2202623747.45922</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2299393395.4761</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2354440.90947713</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2135000.00000031</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2203999.99999991</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2263000.00000004</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2332100.00000035</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2347799.99999971</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2364399.99999936</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2372099.99999966</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2379199.99999979</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2344900.00000062</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2355299.99999999</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2366200.00000065</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2440000.00000051</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2521500.00000044</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2447200.00000019</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2497799.99999954</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2499000.00000014</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2532800.00000029</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2580999.99999971</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2562074.01266265</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2433107.87443401</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2250755.32954556</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2170537.86370219</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2185964.50090536</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2121311.26005411</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>2155379.76837386</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2315709.61387955</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2162267.88553028</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1934100.00000035</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2014399.99999994</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2076300.00000005</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2138600.0000003</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2170799.99999969</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2191299.99999935</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2194599.99999962</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2202499.99999979</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2168800.00000056</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2180199.99999998</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2190200.00000071</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2235300.00000055</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2323700.00000047</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2257000.00000021</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2295599.99999952</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2306200.00000019</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2354500.00000034</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2401999.99999967</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2382885.90362619</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2254903.11108702</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2081942.99141596</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1998671.84578176</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2014080.38260557</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1956352.72405781</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>1983225.90281679</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2133913.64311397</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4157116788.06015</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3918202999.9989</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4072668000.0005</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4284869000.0004</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4400057000.00028</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4434130000.0001</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4274174000.00003</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4282962000.00007</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4410963999.99973</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4113455000.00015</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4127597000.00018</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4326913999.99986</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4449578000.00096</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4575946999.99934</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4454165000.00103</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>4488579999.99975</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>4478093000.00107</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4568795999.99923</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4659400999.99904</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>4621534090.24247</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>4391906228.3783</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>4055965284.58314</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>3914062462.73114</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>3921408518.47882</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>3806027827.0395</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>3845528269.2394</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>4109370153.98039</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3761577773.94317</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2991934999.99897</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3201735999.9999</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3383165000.00053</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3492402999.99986</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3571068000.00043</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3466247999.9997</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3482187999.99971</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3592403999.99936</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3347189000.00015</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3355997000.00008</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3572075999.99994</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3570838000.00105</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3742078999.99918</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3651025000.00092</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3653769999.9997</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3687283000.00129</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3820381999.99918</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3918986999.99909</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>4252414346.69369</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>4020261772.04557</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>3703206609.76558</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>3551174873.2103</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>3557714015.47493</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>3456734429.96188</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>3486541886.2155</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>3732783614.219</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>232362.571663386</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>247639.371562509</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>278077.091061809</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>276541.325425346</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>303099.829185115</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>352757.928952879</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>382535.253755385</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>406712.020413292</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>401014.551955485</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>416403.062595949</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>486177.903983024</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>543525.339049329</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>587680.449696803</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>635543.149603034</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>559003.091237939</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>641483.732139764</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>697086.680225213</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>743262.939657614</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>742256.086210459</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>712758.41872121</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>673648.196354401</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>643232.850408519</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>683777.162308415</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>690245.233210688</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>695414.627876184</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>725178.903586739</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>736850.354685987</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>78069.5851478296</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>83445.1053536972</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>90419.5271452468</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>89978.4537943947</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>98548.2577545835</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>111729.222149449</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>116693.284414281</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>129494.991911644</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>127170.297236136</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>128673.823629995</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>140886.888007287</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>155646.84801278</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>176865.705048684</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>188277.231540522</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>174474.051152227</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>199827.978008729</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>217058.319350043</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>236838.359959911</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>262086.360823724</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>257737.432560524</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>222193.781435508</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>224636.542950735</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>226859.539387775</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>228850.727608539</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>232433.642654016</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>246011.675742251</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>250141.727022035</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
